--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:17</t>
+    <t xml:space="preserve">2026-09-29 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:07</t>
+    <t xml:space="preserve">2026-09-29 18:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -533,7 +533,7 @@
         <v>7.06</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>56.42</v>
+        <v>56.43</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>49.37</v>
@@ -561,10 +561,10 @@
         <v>4.32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>59.54</v>
+        <v>59.53</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>55.21</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>1.41</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>54.23</v>
+        <v>54.24</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>52.83</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2023_valparaiso_provincial.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:44</t>
+    <t xml:space="preserve">2026-10-05 04:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>4.32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>59.53</v>
+        <v>59.54</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>55.22</v>
@@ -606,7 +606,7 @@
         <v>48.92</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>49.18</v>
+        <v>49.19</v>
       </c>
     </row>
   </sheetData>
